--- a/generalization/终极版数据集模板.xlsx
+++ b/generalization/终极版数据集模板.xlsx
@@ -868,7 +868,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>越高越好</t>
+          <t>越低越好</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>越高越好</t>
+          <t>越低越好</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">

--- a/generalization/终极版数据集模板.xlsx
+++ b/generalization/终极版数据集模板.xlsx
@@ -234,6 +234,2346 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing_wm1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm9.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm9.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm9.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm9.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm9.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -520,7 +2860,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -692,11 +3032,12 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -1430,11 +3771,12 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -11206,11 +13548,12 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -26280,11 +28623,12 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -26902,11 +29246,12 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -27332,11 +29677,12 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -29849,11 +32195,12 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -37181,11 +39528,12 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -38483,5 +40831,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/generalization/终极版数据集模板.xlsx
+++ b/generalization/终极版数据集模板.xlsx
@@ -234,2346 +234,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing_wm1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="100000" y="100000"/>
-    <xdr:ext cx="2600000" cy="450000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="AILabel"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2600000" cy="450000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="000000">
-            <a:alpha val="50000"/>
-          </a:srgbClr>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="FFFFFF"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>含 AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="100000" y="100000"/>
-    <xdr:ext cx="2600000" cy="450000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="AILabel"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2600000" cy="450000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="000000">
-            <a:alpha val="50000"/>
-          </a:srgbClr>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="FFFFFF"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>含 AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="100000" y="100000"/>
-    <xdr:ext cx="2600000" cy="450000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="AILabel"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2600000" cy="450000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="000000">
-            <a:alpha val="50000"/>
-          </a:srgbClr>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="FFFFFF"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>含 AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="100000" y="100000"/>
-    <xdr:ext cx="2600000" cy="450000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="AILabel"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2600000" cy="450000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="000000">
-            <a:alpha val="50000"/>
-          </a:srgbClr>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="FFFFFF"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>含 AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="100000" y="100000"/>
-    <xdr:ext cx="2600000" cy="450000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="AILabel"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2600000" cy="450000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="000000">
-            <a:alpha val="50000"/>
-          </a:srgbClr>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="FFFFFF"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>含 AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="100000" y="100000"/>
-    <xdr:ext cx="2600000" cy="450000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="AILabel"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2600000" cy="450000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="000000">
-            <a:alpha val="50000"/>
-          </a:srgbClr>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="FFFFFF"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>含 AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="100000" y="100000"/>
-    <xdr:ext cx="2600000" cy="450000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="AILabel"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2600000" cy="450000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="000000">
-            <a:alpha val="50000"/>
-          </a:srgbClr>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="FFFFFF"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>含 AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="100000" y="100000"/>
-    <xdr:ext cx="2600000" cy="450000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="AILabel"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2600000" cy="450000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="000000">
-            <a:alpha val="50000"/>
-          </a:srgbClr>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="FFFFFF"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>含 AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="100000" y="100000"/>
-    <xdr:ext cx="2600000" cy="450000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="AILabel"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2600000" cy="450000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="000000">
-            <a:alpha val="50000"/>
-          </a:srgbClr>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="FFFFFF"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>含 AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="100000" y="100000"/>
-    <xdr:ext cx="2600000" cy="450000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="AILabel"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2600000" cy="450000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="000000">
-            <a:alpha val="50000"/>
-          </a:srgbClr>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="FFFFFF"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>含 AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="100000" y="100000"/>
-    <xdr:ext cx="2600000" cy="450000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="AILabel"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2600000" cy="450000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="000000">
-            <a:alpha val="50000"/>
-          </a:srgbClr>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="FFFFFF"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>含 AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="100000" y="100000"/>
-    <xdr:ext cx="2600000" cy="450000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="AILabel"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2600000" cy="450000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="000000">
-            <a:alpha val="50000"/>
-          </a:srgbClr>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="FFFFFF"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>含 AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="100000" y="100000"/>
-    <xdr:ext cx="2600000" cy="450000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="AILabel"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2600000" cy="450000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="000000">
-            <a:alpha val="50000"/>
-          </a:srgbClr>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="FFFFFF"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>含 AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="100000" y="100000"/>
-    <xdr:ext cx="2600000" cy="450000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="AILabel"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2600000" cy="450000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="000000">
-            <a:alpha val="50000"/>
-          </a:srgbClr>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="FFFFFF"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>含 AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="100000" y="100000"/>
-    <xdr:ext cx="2600000" cy="450000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="AILabel"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2600000" cy="450000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="000000">
-            <a:alpha val="50000"/>
-          </a:srgbClr>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="FFFFFF"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>含 AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="100000" y="100000"/>
-    <xdr:ext cx="2600000" cy="450000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="AILabel"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2600000" cy="450000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="000000">
-            <a:alpha val="50000"/>
-          </a:srgbClr>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="FFFFFF"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>含 AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="100000" y="100000"/>
-    <xdr:ext cx="2600000" cy="450000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="AILabel"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2600000" cy="450000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="000000">
-            <a:alpha val="50000"/>
-          </a:srgbClr>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="FFFFFF"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>含 AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="100000" y="100000"/>
-    <xdr:ext cx="2600000" cy="450000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="AILabel"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2600000" cy="450000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="000000">
-            <a:alpha val="50000"/>
-          </a:srgbClr>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="FFFFFF"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>含 AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="100000" y="100000"/>
-    <xdr:ext cx="2600000" cy="450000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="AILabel"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2600000" cy="450000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="000000">
-            <a:alpha val="50000"/>
-          </a:srgbClr>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="FFFFFF"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>含 AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="100000" y="100000"/>
-    <xdr:ext cx="2600000" cy="450000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="AILabel"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2600000" cy="450000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="000000">
-            <a:alpha val="50000"/>
-          </a:srgbClr>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="FFFFFF"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>含 AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="100000" y="100000"/>
-    <xdr:ext cx="2600000" cy="450000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="AILabel"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2600000" cy="450000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="000000">
-            <a:alpha val="50000"/>
-          </a:srgbClr>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="FFFFFF"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>含 AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="100000" y="100000"/>
-    <xdr:ext cx="2600000" cy="450000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="AILabel"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2600000" cy="450000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="000000">
-            <a:alpha val="50000"/>
-          </a:srgbClr>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="FFFFFF"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>含 AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="100000" y="100000"/>
-    <xdr:ext cx="2600000" cy="450000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="AILabel"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2600000" cy="450000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="000000">
-            <a:alpha val="50000"/>
-          </a:srgbClr>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="FFFFFF"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>含 AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="100000" y="100000"/>
-    <xdr:ext cx="2600000" cy="450000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="AILabel"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2600000" cy="450000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="000000">
-            <a:alpha val="50000"/>
-          </a:srgbClr>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="FFFFFF"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>含 AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="100000" y="100000"/>
-    <xdr:ext cx="2600000" cy="450000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="AILabel"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2600000" cy="450000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="000000">
-            <a:alpha val="50000"/>
-          </a:srgbClr>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="FFFFFF"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>含 AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm6.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="100000" y="100000"/>
-    <xdr:ext cx="2600000" cy="450000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="AILabel"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2600000" cy="450000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="000000">
-            <a:alpha val="50000"/>
-          </a:srgbClr>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="FFFFFF"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>含 AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm6.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="100000" y="100000"/>
-    <xdr:ext cx="2600000" cy="450000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="AILabel"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2600000" cy="450000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="000000">
-            <a:alpha val="50000"/>
-          </a:srgbClr>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="FFFFFF"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>含 AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm6.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="100000" y="100000"/>
-    <xdr:ext cx="2600000" cy="450000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="AILabel"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2600000" cy="450000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="000000">
-            <a:alpha val="50000"/>
-          </a:srgbClr>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="FFFFFF"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>含 AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm6.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="100000" y="100000"/>
-    <xdr:ext cx="2600000" cy="450000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="AILabel"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2600000" cy="450000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="000000">
-            <a:alpha val="50000"/>
-          </a:srgbClr>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="FFFFFF"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>含 AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm6.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="100000" y="100000"/>
-    <xdr:ext cx="2600000" cy="450000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="AILabel"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2600000" cy="450000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="000000">
-            <a:alpha val="50000"/>
-          </a:srgbClr>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="FFFFFF"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>含 AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm7.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="100000" y="100000"/>
-    <xdr:ext cx="2600000" cy="450000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="AILabel"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2600000" cy="450000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="000000">
-            <a:alpha val="50000"/>
-          </a:srgbClr>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="FFFFFF"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>含 AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm7.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="100000" y="100000"/>
-    <xdr:ext cx="2600000" cy="450000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="AILabel"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2600000" cy="450000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="000000">
-            <a:alpha val="50000"/>
-          </a:srgbClr>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="FFFFFF"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>含 AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm7.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="100000" y="100000"/>
-    <xdr:ext cx="2600000" cy="450000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="AILabel"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2600000" cy="450000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="000000">
-            <a:alpha val="50000"/>
-          </a:srgbClr>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="FFFFFF"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>含 AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm7.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="100000" y="100000"/>
-    <xdr:ext cx="2600000" cy="450000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="AILabel"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2600000" cy="450000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="000000">
-            <a:alpha val="50000"/>
-          </a:srgbClr>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="FFFFFF"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>含 AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm7.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="100000" y="100000"/>
-    <xdr:ext cx="2600000" cy="450000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="AILabel"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2600000" cy="450000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="000000">
-            <a:alpha val="50000"/>
-          </a:srgbClr>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="FFFFFF"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>含 AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm8.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="100000" y="100000"/>
-    <xdr:ext cx="2600000" cy="450000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="AILabel"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2600000" cy="450000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="000000">
-            <a:alpha val="50000"/>
-          </a:srgbClr>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="FFFFFF"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>含 AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm8.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="100000" y="100000"/>
-    <xdr:ext cx="2600000" cy="450000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="AILabel"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2600000" cy="450000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="000000">
-            <a:alpha val="50000"/>
-          </a:srgbClr>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="FFFFFF"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>含 AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm8.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="100000" y="100000"/>
-    <xdr:ext cx="2600000" cy="450000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="AILabel"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2600000" cy="450000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="000000">
-            <a:alpha val="50000"/>
-          </a:srgbClr>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="FFFFFF"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>含 AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm8.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="100000" y="100000"/>
-    <xdr:ext cx="2600000" cy="450000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="AILabel"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2600000" cy="450000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="000000">
-            <a:alpha val="50000"/>
-          </a:srgbClr>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="FFFFFF"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>含 AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm8.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="100000" y="100000"/>
-    <xdr:ext cx="2600000" cy="450000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="AILabel"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2600000" cy="450000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="000000">
-            <a:alpha val="50000"/>
-          </a:srgbClr>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="FFFFFF"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>含 AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm9.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="100000" y="100000"/>
-    <xdr:ext cx="2600000" cy="450000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="AILabel"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2600000" cy="450000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="000000">
-            <a:alpha val="50000"/>
-          </a:srgbClr>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="FFFFFF"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>含 AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm9.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="100000" y="100000"/>
-    <xdr:ext cx="2600000" cy="450000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="AILabel"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2600000" cy="450000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="000000">
-            <a:alpha val="50000"/>
-          </a:srgbClr>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="FFFFFF"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>含 AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm9.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="100000" y="100000"/>
-    <xdr:ext cx="2600000" cy="450000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="AILabel"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2600000" cy="450000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="000000">
-            <a:alpha val="50000"/>
-          </a:srgbClr>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="FFFFFF"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>含 AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm9.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="100000" y="100000"/>
-    <xdr:ext cx="2600000" cy="450000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="AILabel"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2600000" cy="450000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="000000">
-            <a:alpha val="50000"/>
-          </a:srgbClr>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="FFFFFF"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>含 AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm9.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="100000" y="100000"/>
-    <xdr:ext cx="2600000" cy="450000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="AILabel"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2600000" cy="450000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="000000">
-            <a:alpha val="50000"/>
-          </a:srgbClr>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="FFFFFF"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>含 AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2860,7 +520,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -3032,12 +692,11 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -3771,12 +1430,11 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -5821,7 +3479,7 @@
         </is>
       </c>
       <c r="H15" s="5" t="n">
-        <v>60</v>
+        <v>71.5</v>
       </c>
       <c r="I15" s="7" t="n">
         <v>1.08</v>
@@ -5956,7 +3614,7 @@
         </is>
       </c>
       <c r="H16" s="5" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="I16" s="6" t="n">
         <v>1.08</v>
@@ -6091,7 +3749,7 @@
         </is>
       </c>
       <c r="H17" s="5" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="I17" s="7" t="n">
         <v>1.08</v>
@@ -6226,7 +3884,7 @@
         </is>
       </c>
       <c r="H18" s="5" t="n">
-        <v>50</v>
+        <v>51.3</v>
       </c>
       <c r="I18" s="6" t="n">
         <v>1.07</v>
@@ -6481,12 +4139,12 @@
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>固化剂</t>
+          <t>树脂</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>酚醛</t>
+          <t>环氧</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr"/>
@@ -6505,19 +4163,19 @@
         <v>950</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="L20" s="5" t="n">
         <v>1</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>350</v>
+        <v>30</v>
       </c>
       <c r="N20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P20" s="6" t="n">
         <v>70</v>
@@ -6547,10 +4205,10 @@
         <v>74</v>
       </c>
       <c r="Y20" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z20" s="6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA20" s="6" t="n">
         <v>0</v>
@@ -6562,10 +4220,10 @@
         <v>0</v>
       </c>
       <c r="AD20" s="5" t="n">
-        <v>0</v>
+        <v>0.155</v>
       </c>
       <c r="AE20" s="5" t="n">
-        <v>0.206</v>
+        <v>0.018</v>
       </c>
       <c r="AF20" s="5" t="n">
         <v>0.002</v>
@@ -6580,10 +4238,10 @@
         <v>0</v>
       </c>
       <c r="AJ20" s="5" t="n">
-        <v>0.6</v>
+        <v>0.45</v>
       </c>
       <c r="AK20" s="5" t="n">
-        <v>0.05</v>
+        <v>0.12</v>
       </c>
       <c r="AL20" s="6" t="n">
         <v>0</v>
@@ -6631,7 +4289,7 @@
         </is>
       </c>
       <c r="H21" s="5" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="I21" s="7" t="n">
         <v>1.1</v>
@@ -6901,7 +4559,7 @@
         </is>
       </c>
       <c r="H23" s="5" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="I23" s="7" t="n">
         <v>1.1</v>
@@ -7426,12 +5084,12 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>树脂</t>
+          <t>助剂</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>丙烯酸</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr"/>
@@ -7441,7 +5099,7 @@
         </is>
       </c>
       <c r="H27" s="5" t="n">
-        <v>50</v>
+        <v>99</v>
       </c>
       <c r="I27" s="7" t="n">
         <v>1.05</v>
@@ -7462,10 +5120,10 @@
         <v>0</v>
       </c>
       <c r="O27" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P27" s="7" t="n">
-        <v>45</v>
+        <v>-10</v>
       </c>
       <c r="Q27" s="7" t="n">
         <v>250</v>
@@ -7489,13 +5147,13 @@
         <v>0</v>
       </c>
       <c r="X27" s="7" t="n">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="Y27" s="7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z27" s="7" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="AA27" s="7" t="n">
         <v>0</v>
@@ -7507,7 +5165,7 @@
         <v>0</v>
       </c>
       <c r="AD27" s="5" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="AE27" s="5" t="n">
         <v>0.03</v>
@@ -7516,7 +5174,7 @@
         <v>0.003</v>
       </c>
       <c r="AG27" s="5" t="n">
-        <v>0.3</v>
+        <v>0.11</v>
       </c>
       <c r="AH27" s="5" t="n">
         <v>0</v>
@@ -7566,7 +5224,7 @@
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>丙烯酸</t>
+          <t>乙烯基</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr"/>
@@ -7576,13 +5234,13 @@
         </is>
       </c>
       <c r="H28" s="5" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I28" s="6" t="n">
         <v>1.05</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>15000</v>
+        <v>60000</v>
       </c>
       <c r="K28" s="5" t="n">
         <v>0</v>
@@ -7597,10 +5255,10 @@
         <v>0</v>
       </c>
       <c r="O28" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="Q28" s="6" t="n">
         <v>250</v>
@@ -7624,13 +5282,13 @@
         <v>0</v>
       </c>
       <c r="X28" s="6" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="Y28" s="6" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Z28" s="6" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AA28" s="6" t="n">
         <v>0</v>
@@ -7639,7 +5297,7 @@
         <v>0</v>
       </c>
       <c r="AC28" s="6" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AD28" s="5" t="n">
         <v>0</v>
@@ -7651,7 +5309,7 @@
         <v>0.003</v>
       </c>
       <c r="AG28" s="5" t="n">
-        <v>0.3</v>
+        <v>0.01</v>
       </c>
       <c r="AH28" s="5" t="n">
         <v>0</v>
@@ -7660,7 +5318,7 @@
         <v>0</v>
       </c>
       <c r="AJ28" s="5" t="n">
-        <v>0.25</v>
+        <v>0.02</v>
       </c>
       <c r="AK28" s="5" t="n">
         <v>0.05</v>
@@ -7696,12 +5354,12 @@
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>树脂</t>
+          <t>助剂</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>丙烯酸</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr"/>
@@ -7711,13 +5369,13 @@
         </is>
       </c>
       <c r="H29" s="5" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I29" s="7" t="n">
         <v>1.05</v>
       </c>
       <c r="J29" s="7" t="n">
-        <v>15000</v>
+        <v>400</v>
       </c>
       <c r="K29" s="5" t="n">
         <v>0</v>
@@ -7732,10 +5390,10 @@
         <v>0</v>
       </c>
       <c r="O29" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P29" s="7" t="n">
-        <v>45</v>
+        <v>-5</v>
       </c>
       <c r="Q29" s="7" t="n">
         <v>250</v>
@@ -7759,13 +5417,13 @@
         <v>0</v>
       </c>
       <c r="X29" s="7" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="Y29" s="7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z29" s="7" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="AA29" s="7" t="n">
         <v>0</v>
@@ -7780,13 +5438,13 @@
         <v>0</v>
       </c>
       <c r="AE29" s="5" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="AF29" s="5" t="n">
         <v>0.003</v>
       </c>
       <c r="AG29" s="5" t="n">
-        <v>0.3</v>
+        <v>0.11</v>
       </c>
       <c r="AH29" s="5" t="n">
         <v>0</v>
@@ -7801,7 +5459,7 @@
         <v>0.05</v>
       </c>
       <c r="AL29" s="7" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AM29" s="7" t="n">
         <v>0</v>
@@ -7831,12 +5489,12 @@
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>树脂</t>
+          <t>助剂</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>丙烯酸</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr"/>
@@ -7846,13 +5504,13 @@
         </is>
       </c>
       <c r="H30" s="5" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="I30" s="6" t="n">
         <v>1.05</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>15000</v>
+        <v>500</v>
       </c>
       <c r="K30" s="5" t="n">
         <v>0</v>
@@ -7867,10 +5525,10 @@
         <v>0</v>
       </c>
       <c r="O30" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>45</v>
+        <v>-10</v>
       </c>
       <c r="Q30" s="6" t="n">
         <v>250</v>
@@ -7894,13 +5552,13 @@
         <v>0</v>
       </c>
       <c r="X30" s="6" t="n">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="Y30" s="6" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="Z30" s="6" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="AA30" s="6" t="n">
         <v>0</v>
@@ -7936,7 +5594,7 @@
         <v>0.05</v>
       </c>
       <c r="AL30" s="6" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AM30" s="6" t="n">
         <v>0</v>
@@ -10459,13 +8117,13 @@
         </is>
       </c>
       <c r="H49" s="5" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="I49" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J49" s="7" t="n">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="K49" s="5" t="n">
         <v>0</v>
@@ -10510,13 +8168,13 @@
         <v>65</v>
       </c>
       <c r="Y49" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z49" s="7" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AA49" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB49" s="7" t="n">
         <v>0</v>
@@ -10729,7 +8387,7 @@
         </is>
       </c>
       <c r="H51" s="5" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="I51" s="7" t="n">
         <v>1</v>
@@ -10750,10 +8408,10 @@
         <v>0</v>
       </c>
       <c r="O51" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P51" s="7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Q51" s="7" t="n">
         <v>300</v>
@@ -10777,13 +8435,13 @@
         <v>0</v>
       </c>
       <c r="X51" s="7" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="Y51" s="7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z51" s="7" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="AA51" s="7" t="n">
         <v>0</v>
@@ -10798,13 +8456,13 @@
         <v>0</v>
       </c>
       <c r="AE51" s="5" t="n">
-        <v>0.024</v>
+        <v>0.02</v>
       </c>
       <c r="AF51" s="5" t="n">
         <v>0.003</v>
       </c>
       <c r="AG51" s="5" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="AH51" s="5" t="n">
         <v>0</v>
@@ -10864,7 +8522,7 @@
         </is>
       </c>
       <c r="H52" s="5" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="I52" s="6" t="n">
         <v>1</v>
@@ -10885,7 +8543,7 @@
         <v>0</v>
       </c>
       <c r="O52" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P52" s="6" t="n">
         <v>20</v>
@@ -10912,13 +8570,13 @@
         <v>0</v>
       </c>
       <c r="X52" s="6" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="Y52" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z52" s="6" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="AA52" s="6" t="n">
         <v>0</v>
@@ -10939,7 +8597,7 @@
         <v>0.003</v>
       </c>
       <c r="AG52" s="5" t="n">
-        <v>0.2</v>
+        <v>0.12</v>
       </c>
       <c r="AH52" s="5" t="n">
         <v>0</v>
@@ -10999,7 +8657,7 @@
         </is>
       </c>
       <c r="H53" s="5" t="n">
-        <v>100</v>
+        <v>12.5</v>
       </c>
       <c r="I53" s="7" t="n">
         <v>1</v>
@@ -11047,13 +8705,13 @@
         <v>0</v>
       </c>
       <c r="X53" s="7" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="Y53" s="7" t="n">
         <v>9</v>
       </c>
       <c r="Z53" s="7" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AA53" s="7" t="n">
         <v>0</v>
@@ -11086,7 +8744,7 @@
         <v>0.2</v>
       </c>
       <c r="AK53" s="5" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="AL53" s="7" t="n">
         <v>0</v>
@@ -11659,7 +9317,7 @@
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>助剂</t>
+          <t>颜料</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
@@ -11674,7 +9332,7 @@
         </is>
       </c>
       <c r="H58" s="5" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="I58" s="6" t="n">
         <v>1</v>
@@ -11722,13 +9380,13 @@
         <v>0</v>
       </c>
       <c r="X58" s="6" t="n">
-        <v>65</v>
+        <v>10</v>
       </c>
       <c r="Y58" s="6" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Z58" s="6" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="AA58" s="6" t="n">
         <v>0</v>
@@ -11767,7 +9425,7 @@
         <v>0</v>
       </c>
       <c r="AM58" s="6" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AN58" s="6" t="inlineStr">
         <is>
@@ -11794,12 +9452,12 @@
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>助剂</t>
+          <t>固化剂</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>氨基</t>
         </is>
       </c>
       <c r="F59" s="7" t="inlineStr"/>
@@ -11809,7 +9467,7 @@
         </is>
       </c>
       <c r="H59" s="5" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="I59" s="7" t="n">
         <v>1</v>
@@ -11830,10 +9488,10 @@
         <v>0</v>
       </c>
       <c r="O59" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P59" s="7" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="Q59" s="7" t="n">
         <v>300</v>
@@ -11857,16 +9515,16 @@
         <v>0</v>
       </c>
       <c r="X59" s="7" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="Y59" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z59" s="7" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AA59" s="7" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AB59" s="7" t="n">
         <v>0</v>
@@ -11878,22 +9536,22 @@
         <v>0</v>
       </c>
       <c r="AE59" s="5" t="n">
-        <v>0.024</v>
+        <v>0.05</v>
       </c>
       <c r="AF59" s="5" t="n">
         <v>0.003</v>
       </c>
       <c r="AG59" s="5" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="AH59" s="5" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="AI59" s="5" t="n">
         <v>0.05</v>
       </c>
       <c r="AJ59" s="5" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="AK59" s="5" t="n">
         <v>0.1</v>
@@ -11929,12 +9587,12 @@
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>助剂</t>
+          <t>固化剂</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>氨基</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr"/>
@@ -11944,7 +9602,7 @@
         </is>
       </c>
       <c r="H60" s="5" t="n">
-        <v>100</v>
+        <v>99.5</v>
       </c>
       <c r="I60" s="6" t="n">
         <v>1</v>
@@ -11965,10 +9623,10 @@
         <v>0</v>
       </c>
       <c r="O60" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P60" s="6" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="Q60" s="6" t="n">
         <v>300</v>
@@ -11992,17 +9650,17 @@
         <v>0</v>
       </c>
       <c r="X60" s="6" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Y60" s="6" t="n">
         <v>9</v>
       </c>
       <c r="Z60" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA60" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="AA60" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="AB60" s="6" t="n">
         <v>0</v>
       </c>
@@ -12013,22 +9671,22 @@
         <v>0</v>
       </c>
       <c r="AE60" s="5" t="n">
-        <v>0.024</v>
+        <v>0.04</v>
       </c>
       <c r="AF60" s="5" t="n">
         <v>0.003</v>
       </c>
       <c r="AG60" s="5" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="AH60" s="5" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="AI60" s="5" t="n">
         <v>0.05</v>
       </c>
       <c r="AJ60" s="5" t="n">
-        <v>0.2</v>
+        <v>0.12</v>
       </c>
       <c r="AK60" s="5" t="n">
         <v>0.1</v>
@@ -12064,12 +9722,12 @@
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>助剂</t>
+          <t>固化剂</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>氨基</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr"/>
@@ -12079,7 +9737,7 @@
         </is>
       </c>
       <c r="H61" s="5" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I61" s="7" t="n">
         <v>1</v>
@@ -12100,10 +9758,10 @@
         <v>0</v>
       </c>
       <c r="O61" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P61" s="7" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="Q61" s="7" t="n">
         <v>300</v>
@@ -12127,16 +9785,16 @@
         <v>0</v>
       </c>
       <c r="X61" s="7" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Y61" s="7" t="n">
         <v>9</v>
       </c>
       <c r="Z61" s="7" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AA61" s="7" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AB61" s="7" t="n">
         <v>0</v>
@@ -12148,22 +9806,22 @@
         <v>0</v>
       </c>
       <c r="AE61" s="5" t="n">
-        <v>0.024</v>
+        <v>0.04</v>
       </c>
       <c r="AF61" s="5" t="n">
         <v>0.003</v>
       </c>
       <c r="AG61" s="5" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="AH61" s="5" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AI61" s="5" t="n">
         <v>0.05</v>
       </c>
       <c r="AJ61" s="5" t="n">
-        <v>0.2</v>
+        <v>0.08</v>
       </c>
       <c r="AK61" s="5" t="n">
         <v>0.1</v>
@@ -12743,12 +10401,12 @@
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>颜料</t>
+          <t>树脂</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>聚氨酯</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr"/>
@@ -12758,7 +10416,7 @@
         </is>
       </c>
       <c r="H66" s="5" t="n">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="I66" s="6" t="n">
         <v>4</v>
@@ -12779,10 +10437,10 @@
         <v>0</v>
       </c>
       <c r="O66" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P66" s="6" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q66" s="6" t="n">
         <v>500</v>
@@ -12806,17 +10464,17 @@
         <v>0</v>
       </c>
       <c r="X66" s="6" t="n">
+        <v>70</v>
+      </c>
+      <c r="Y66" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z66" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA66" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="Y66" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z66" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="AA66" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="AB66" s="6" t="n">
         <v>0</v>
       </c>
@@ -12833,16 +10491,16 @@
         <v>0</v>
       </c>
       <c r="AG66" s="5" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="AH66" s="5" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AI66" s="5" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="AJ66" s="5" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AK66" s="5" t="n">
         <v>0</v>
@@ -12851,7 +10509,7 @@
         <v>0</v>
       </c>
       <c r="AM66" s="6" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AN66" s="6" t="inlineStr">
         <is>
@@ -12878,12 +10536,12 @@
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>颜料</t>
+          <t>树脂</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>聚氨酯</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr"/>
@@ -12893,7 +10551,7 @@
         </is>
       </c>
       <c r="H67" s="5" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="I67" s="7" t="n">
         <v>4</v>
@@ -12914,10 +10572,10 @@
         <v>0</v>
       </c>
       <c r="O67" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P67" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q67" s="7" t="n">
         <v>500</v>
@@ -12941,16 +10599,16 @@
         <v>0</v>
       </c>
       <c r="X67" s="7" t="n">
-        <v>10</v>
+        <v>68</v>
       </c>
       <c r="Y67" s="7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z67" s="7" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AA67" s="7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AB67" s="7" t="n">
         <v>0</v>
@@ -12968,16 +10626,16 @@
         <v>0</v>
       </c>
       <c r="AG67" s="5" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="AH67" s="5" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="AI67" s="5" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="AJ67" s="5" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AK67" s="5" t="n">
         <v>0</v>
@@ -12986,7 +10644,7 @@
         <v>0</v>
       </c>
       <c r="AM67" s="7" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AN67" s="7" t="inlineStr">
         <is>
@@ -13548,12 +11206,11 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -28623,12 +26280,11 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -29246,12 +26902,11 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -29677,12 +27332,11 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -32195,12 +29849,11 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -39528,12 +37181,11 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -39924,7 +37576,7 @@
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>环氧/酚醛/聚酯/乙烯基/丙烯酸/聚氨酯/其他</t>
+          <t>环氧/酚醛/聚酯/乙烯基/丙烯酸/聚氨酯/氨基/其他</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -40831,6 +38483,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>